--- a/blendmaster-backend/input/data.xlsx
+++ b/blendmaster-backend/input/data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BlendMaster\file mappings\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BlendMaster\blendmaster-backend\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{265BB3FE-2542-45B8-9E9A-172A6CAE2B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4395A994-2837-40BC-8F8C-FDB55E5BDE36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="-3435" windowWidth="25800" windowHeight="21000" tabRatio="685" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-37530" yWindow="-21780" windowWidth="51840" windowHeight="21240" tabRatio="685" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="final_input_equipment_data" sheetId="6" r:id="rId1"/>
@@ -711,6 +711,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.77734375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -751,7 +752,7 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>50000</v>
+        <v>10000</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -783,7 +784,7 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>50000</v>
+        <v>5000</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -815,7 +816,7 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>50000</v>
+        <v>4000</v>
       </c>
       <c r="C4">
         <v>3</v>

--- a/blendmaster-backend/input/data.xlsx
+++ b/blendmaster-backend/input/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BlendMaster\blendmaster-backend\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4395A994-2837-40BC-8F8C-FDB55E5BDE36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDD0275A-D3DA-4AA2-8260-039B8A8D6DFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-37530" yWindow="-21780" windowWidth="51840" windowHeight="21240" tabRatio="685" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-11610" yWindow="-21660" windowWidth="25800" windowHeight="21000" tabRatio="685" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="final_input_equipment_data" sheetId="6" r:id="rId1"/>
@@ -621,19 +621,19 @@
         <v>6000</v>
       </c>
       <c r="D2">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E2">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F2">
         <v>6000</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H2">
-        <v>61.5</v>
+        <v>59</v>
       </c>
       <c r="I2">
         <v>6000</v>
@@ -710,7 +710,9 @@
   <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.77734375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>

--- a/blendmaster-backend/input/data.xlsx
+++ b/blendmaster-backend/input/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BlendMaster\blendmaster-backend\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDD0275A-D3DA-4AA2-8260-039B8A8D6DFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DACFC551-8B30-4FBB-9899-8654D3004F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-11610" yWindow="-21660" windowWidth="25800" windowHeight="21000" tabRatio="685" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14070" yWindow="-21720" windowWidth="51840" windowHeight="21240" tabRatio="685" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="final_input_equipment_data" sheetId="6" r:id="rId1"/>
@@ -18,12 +18,25 @@
     <sheet name="final_input_grade_block_data" sheetId="9" r:id="rId3"/>
     <sheet name="final_input_stockpile_data" sheetId="10" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="32">
   <si>
     <t>name</t>
   </si>
@@ -110,16 +123,31 @@
   </si>
   <si>
     <t>use</t>
+  </si>
+  <si>
+    <t>SP4</t>
+  </si>
+  <si>
+    <t>SP5</t>
+  </si>
+  <si>
+    <t>SP6</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -671,7 +699,7 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>50000</v>
+        <v>20000</v>
       </c>
       <c r="C2" t="b">
         <v>1</v>
@@ -680,7 +708,7 @@
         <v>15</v>
       </c>
       <c r="E2">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -688,7 +716,7 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>50000</v>
+        <v>20000</v>
       </c>
       <c r="C3" t="b">
         <v>1</v>
@@ -697,17 +725,18 @@
         <v>15</v>
       </c>
       <c r="E3">
-        <v>57.5</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
@@ -754,7 +783,7 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -778,7 +807,7 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -786,7 +815,7 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>5000</v>
+        <v>20000</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -810,7 +839,7 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -818,7 +847,7 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>4000</v>
+        <v>20000</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -842,10 +871,107 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>60</v>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5">
+        <v>20000</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5">
+        <v>25000</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6">
+        <v>20000</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6">
+        <v>25000</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7">
+        <v>20000</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7">
+        <v>25000</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>